--- a/AI Audit Log_NguyenThiAnThuyen.xlsx
+++ b/AI Audit Log_NguyenThiAnThuyen.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\swd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DD2C6B-6D2C-4918-B68D-9F263EAF9FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9953BB17-EC38-4D6F-B901-59687996B615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="week1" sheetId="2" r:id="rId2"/>
+    <sheet name="week2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -130,6 +129,86 @@
   <si>
     <t>Phản hồi: AI dùng ví dụ xây quán cà phê để giải thích toàn bộ: Kiến trúc = bản vẽ mặt bằng; Mô hình hóa = bản vẽ chi tiết điện nước; SDLC = quy trình từ ý tưởng đến khai trương.
 Quyết định: Tôi đánh giá cách tiếp cận này hiệu quả hơn hẳn so với định nghĩa kỹ thuật thuần túy. Tôi giữ lại phép so sánh 'quán cà phê' làm công cụ ôn tập và giải thích cho người khác. Đây là kỹ thuật Analogy — rất hữu ích khi học khái niệm trừu tượng.</t>
+  </si>
+  <si>
+    <t>Nhận diện kiến trúc Use Case</t>
+  </si>
+  <si>
+    <t>"Tìm hiểu về use case theo các mục: Requirement Modeling Use Cases, Identifying Use Cases, Documenting Use Cases, Activity Diagrams"</t>
+  </si>
+  <si>
+    <t>AI trình bày tổng quan 4 thành phần: mô hình hóa yêu cầu, xác định use case, đặc tả dạng template, và vẽ activity diagram kèm sơ đồ minh họa.
+Quyết định: Tôi nhận ra AI trình bày đúng cấu trúc học Use Case. Tôi chọn giữ toàn bộ nội dung vì bao quát đủ 4 giai đoạn cần học.</t>
+  </si>
+  <si>
+    <t>Lọc thông tin cốt lõi</t>
+  </si>
+  <si>
+    <t>Là một sinh viên IT tôi cần học viết use case bắt đầu từ đâu, có cách nào để dễ hiểu và tránh được những lỗi thường gặp khi vẽ use case</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đưa ra lộ trình 4 bước học (tư duy → template → diagram → checklist) và liệt kê các lỗi phổ biến theo nhóm: đặt tên, xác định actor, quan hệ include/extend, đặc tả template.
+Kiểm chứng: AI trình bày chính xác. Tôi xác nhận các lỗi include/extend ngược chiều là lỗi tôi hay mắc phải. Tôi quyết định lưu checklist lỗi này để tự kiểm tra khi vẽ.</t>
+  </si>
+  <si>
+    <t>Quy trình tài liệu hóa</t>
+  </si>
+  <si>
+    <t>Tôi quan sát cách AI mô tả luồng chính (Main Flow) trong template use case UC02: Đặt hàng gồm 6 bước tuần tự.</t>
+  </si>
+  <si>
+    <t>AI trình bày đúng cấu trúc template chuẩn: ID, tên, actor, mô tả, tiền điều kiện, hậu điều kiện, luồng chính, luồng thay thế, ngoại lệ.
+Kiểm chứng: Tôi nhận thấy luồng chính chỉ có happy path, không chứa if/else — đây là điểm tôi chưa nắm. Tôi quyết định áp dụng đúng cách này khi viết đặc tả bài tập.</t>
+  </si>
+  <si>
+    <t>Nhận diện mối quan hệ include/extend</t>
+  </si>
+  <si>
+    <t>Tôi tiếp nhận phần giải thích quan hệ «include» và «extend» trong Use Case Diagram, kèm trick ghi nhớ: include = gọi hàm bắt buộc, extend = override có điều kiện.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích rõ chiều mũi tên và khi nào dùng từng loại quan hệ.
+Kiểm chứng: Tôi kiểm tra lại diagram đã vẽ trước đây — phát hiện tôi từng vẽ mũi tên «include» ngược chiều. Tôi đã sửa lại và ghi chú trick nhớ vào tài liệu cá nhân.</t>
+  </si>
+  <si>
+    <t>Nhận diện danh mục câu hỏi phân tích</t>
+  </si>
+  <si>
+    <t>"Các câu hỏi để xác định actor và use case"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân loại thành 3 nhóm câu hỏi có cấu trúc: (1) Câu hỏi tìm Actor gồm 4 nhóm nhỏ — ai tương tác trực tiếp, ai quản lý, hệ thống ngoài nào tham gia, phân biệt vai trò; (2) Câu hỏi tìm Use Case gồm 4 nhóm — mục tiêu actor, sự kiện kích hoạt, ranh giới phạm vi, kiểm tra đủ/không thừa; (3) Câu hỏi kiểm tra lại toàn bộ.
+Quyết định: Tôi nhận ra đây là pattern tư duy phân tích có hệ thống. Tôi chọn lưu lại bộ câu hỏi này làm checklist cá nhân khi bắt đầu phân tích bất kỳ hệ thống nào.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đưa ra template câu đơn giản giúp chuyển mục tiêu của actor thành tên use case. Ví dụ: "Khách hàng muốn theo dõi đơn hàng để biết thời gian giao hàng" → Use case: Theo dõi trạng thái đơn hàng.
+Kiểm chứng: Tôi tự thử với hệ thống thư viện — "Sinh viên muốn mượn sách để đọc tài liệu" → Use case: Mượn sách. Kết quả đúng và tự nhiên. Tôi quyết định dùng template này thay vì đoán tên use case trực tiếp.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp tiêu chí phân biệt rõ: actor phải là thực thể bên ngoài hệ thống (người hoặc hệ thống khác), tên phải là vai trò (role), không phải tên cá nhân hay tên module nội bộ.
+Kiểm chứng: Tôi xem lại bài thực hành cũ — tôi đã từng đặt "Module xác thực" làm actor. Đây là sai vì đó là thành phần bên trong hệ thống. Tôi đã sửa lại thành actor "Người dùng".</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chỉ ra ranh giới quan trọng: use case phải là mục tiêu từ góc nhìn actor, không phải hành động xử lý nội bộ của hệ thống.
+Kiểm chứng: Tôi nhận ra lỗi mình hay mắc — đặt tên use case theo góc nhìn lập trình viên ("Validate dữ liệu", "Lưu database") thay vì góc nhìn người dùng. Tôi quyết định luôn hỏi "Actor có thấy và quan tâm đến việc này không?" trước khi đặt tên use case.</t>
+  </si>
+  <si>
+    <t>Nhận diện use case không hợp lệ</t>
+  </si>
+  <si>
+    <t>Tôi đọc câu hỏi kiểm tra: "Use case này mô tả mục tiêu của actor, không phải bước xử lý của hệ thống?" với ví dụ sai: "Kiểm tra tồn kho" và đúng: "Xem tình trạng sản phẩm".</t>
+  </si>
+  <si>
+    <t>Tôi quan sát câu hỏi kiểm tra: "Actor này nằm ngoài hệ thống, không phải module bên trong?" và "Actor có tên là vai trò, không phải tên người cụ thể?"</t>
+  </si>
+  <si>
+    <t>Phân biệt actor hợp lệ và không hợp lệ</t>
+  </si>
+  <si>
+    <t>Lọc nguyên tắc cốt lõi</t>
+  </si>
+  <si>
+    <t>Tôi tiếp nhận mẹo thực tế: viết câu theo mẫu "[Actor] muốn [động từ] [đối tượng] để [mục đích]" để tìm use case.</t>
   </si>
 </sst>
 </file>
@@ -734,18 +813,143 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.19921875" customWidth="1"/>
+    <col min="2" max="2" width="25.19921875" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="55.796875" customWidth="1"/>
+    <col min="5" max="5" width="26.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="69" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="69" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AI Audit Log_NguyenThiAnThuyen.xlsx
+++ b/AI Audit Log_NguyenThiAnThuyen.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\swd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9953BB17-EC38-4D6F-B901-59687996B615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8F8F5E-9470-4CD4-943E-742D0061542A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="week1" sheetId="2" r:id="rId2"/>
     <sheet name="week2" sheetId="3" r:id="rId3"/>
+    <sheet name="week3" sheetId="4" r:id="rId4"/>
+    <sheet name="week4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -209,6 +211,46 @@
   </si>
   <si>
     <t>Tôi tiếp nhận mẹo thực tế: viết câu theo mẫu "[Actor] muốn [động từ] [đối tượng] để [mục đích]" để tìm use case.</t>
+  </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>Process/Algorithm</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>Abstraction + Decomposition</t>
+  </si>
+  <si>
+    <t>"Tôi đang thiết kế class diagram cho hệ thống quản lý thư viện. Hãy liệt kê các thuộc tính cần thiết cho class Book."</t>
+  </si>
+  <si>
+    <t>"Viết phương thức checkOut() cho class LoanRecord trong hệ thống thư viện. Xử lý khi sách đã hết hoặc thành viên quá hạn."</t>
+  </si>
+  <si>
+    <t>"So sánh việc dùng Composition vs Aggregation cho quan hệ giữa LibraryBranch và BookCopy. Nên dùng loại nào?"</t>
+  </si>
+  <si>
+    <t>"Hãy xác định các class cần thiết và quan hệ giữa chúng cho module đăng ký mượn sách online (Member tự đặt trước qua web)."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất 5 class: Member, Book, Reservation, Notification, ReservationQueue với quan hệ đầy đủ.
+Kiểm chứng: Tôi nhận thấy AI gộp logic hàng đợi vào Reservation thay vì tách riêng (God Class). Tôi yêu cầu tách thành ReservationService chứa business logic, giữ Reservation là entity thuần tuý. Áp dụng nguyên tắc Single Responsibility: mỗi class chỉ có một lý do để thay đổi.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI gợi ý Strategy Pattern với interface INotificationSender và 3 concrete class: EmailSender, SmsSender, PushSender.
+Kiểm chứng: Tôi tra cứu thêm trên refactoring.guru và nhận ra AI bỏ sót Observer Pattern — phù hợp hơn khi Notification cần lắng nghe sự kiện từ nhiều module. Tôi quyết định kết hợp cả hai: Observer để trigger, Strategy để chọn kênh gửi, và ghi chú rõ stereotype «interface» và «abstract» trong diagram.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp signature: + checkOut(memberId: Long, bookId: Long): boolean và mô tả logic cơ bản.
+Kiểm chứng: Tôi nhận thấy AI bỏ sót trường hợp member đang bị khoá tài khoản (Oversimplification). Tôi yêu cầu AI bổ sung điều kiện kiểm tra member.isActive() trước khi xử lý, và cập nhật lại returnType thành LoanResult (enum) thay vì boolean để phân biệt từng lý do thất bại.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê 15 thuộc tính gồm id, title, author, isbn, publisher, publishYear, genre, language, pageCount, price, stock, location, status, coverImage, description.
+Quyết định: Tôi chỉ giữ lại 8 thuộc tính cốt lõi (id, title, author, isbn, publishYear, stock, status, location) vì đây là MVP — các trường như coverImage và description chỉ cần ở tầng UI, không cần mô hình hoá trong class diagram.</t>
   </si>
 </sst>
 </file>
@@ -268,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -290,6 +332,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -952,4 +997,176 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239A1066-2C51-452D-B370-AFF4D9A6B185}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.3984375" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="29.3984375" customWidth="1"/>
+    <col min="4" max="4" width="58.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C248E5C9-22F0-4900-8DE2-0E9ECEA68BB6}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24.8984375" customWidth="1"/>
+    <col min="3" max="3" width="35.59765625" customWidth="1"/>
+    <col min="4" max="4" width="57.09765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="117.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="107.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="155.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenThiAnThuyen.xlsx
+++ b/AI Audit Log_NguyenThiAnThuyen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\swd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8F8F5E-9470-4CD4-943E-742D0061542A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54EE732-AF8A-4F19-9981-723E03CDBFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="week2" sheetId="3" r:id="rId3"/>
     <sheet name="week3" sheetId="4" r:id="rId4"/>
     <sheet name="week4" sheetId="5" r:id="rId5"/>
+    <sheet name="week5" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="77">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -251,6 +252,44 @@
   <si>
     <t>Phản hồi: AI liệt kê 15 thuộc tính gồm id, title, author, isbn, publisher, publishYear, genre, language, pageCount, price, stock, location, status, coverImage, description.
 Quyết định: Tôi chỉ giữ lại 8 thuộc tính cốt lõi (id, title, author, isbn, publishYear, stock, status, location) vì đây là MVP — các trường như coverImage và description chỉ cần ở tầng UI, không cần mô hình hoá trong class diagram.</t>
+  </si>
+  <si>
+    <t>Nhận diện kiến trúc biểu đồ trạng thái</t>
+  </si>
+  <si>
+    <t>"Tìm hiểu về biểu đồ trạng thái (State Diagram) theo các mục: định nghĩa, các ký hiệu cơ bản, khi nào nên dùng, và ví dụ minh họa thực tế"</t>
+  </si>
+  <si>
+    <t>Nhận diện mối quan hệ giữa các trạng thái</t>
+  </si>
+  <si>
+    <t>Vận dụng &amp; kiểm chứng</t>
+  </si>
+  <si>
+    <t>Hãy giúp tôi vẽ biểu đồ trạng thái cho một hệ thống đặt phòng khách sạn với các trạng thái: Trống, Đã đặt, Đã nhận phòng, Đang dọn dẹp. Bao gồm đầy đủ guard condition và điểm đầu/cuối.</t>
+  </si>
+  <si>
+    <t>Tôi tiếp nhận phần giải thích sự khác biệt giữa biểu đồ trạng thái và flowchart trong UML, kèm trick ghi nhớ: State Diagram = vòng đời của đối tượng; Flowchart = luồng công việc/quy trình.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tạo biểu đồ trạng thái đầy đủ với 4 trạng thái, các chuyển tiếp có tên sự kiện rõ ràng (bookRoom, checkIn, checkOut, cleaningDone), guard condition [room available] trên sự kiện bookRoom, điểm khởi đầu và điểm kết thúc.
+Kiểm chứng: Tôi tự vẽ lại biểu đồ tay và đối chiếu — phát hiện tôi quên thêm điểm kết thúc sau trạng thái Trống khi phòng bị loại khỏi hệ thống. Tôi bổ sung thêm transition này và xác nhận biểu đồ hoàn chỉnh, đúng chuẩn UML.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích rõ biểu đồ trạng thái mô tả đối tượng *đang ở đâu* trong vòng đời, còn flowchart mô tả *làm gì* theo trình tự. Ví dụ: "Đơn hàng đang ở trạng thái Đã thanh toán" là state diagram; "Hệ thống xử lý thanh toán theo 5 bước" là flowchart.
+Kiểm chứng: Tôi kiểm tra lại bài tập sơ đồ trước — phát hiện tôi từng dùng tên trạng thái mô tả hành động thay vì trạng thái tồn tại. Tôi đã sửa lại và ghi chú trick nhớ vào tài liệu cá nhân.</t>
+  </si>
+  <si>
+    <t>AI trình bày đúng cấu trúc ký hiệu chuẩn UML: mỗi ký hiệu có tên, hình dạng, và mục đích sử dụng cụ thể. Ví dụ minh họa vòng đời đơn hàng (Chờ xử lý → Đã thanh toán → Đang giao → Hoàn thành) áp dụng đầy đủ 5 ký hiệu.
+Kiểm chứng: Tôi nhận thấy guard condition [điều kiện] thường bị bỏ quên khi cùng một sự kiện dẫn đến hai trạng thái khác nhau — đây là điểm tôi chưa nắm. Tôi quyết định áp dụng đúng cách này khi vẽ bài tập.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đưa ra lộ trình 6 bước học (xác định đối tượng → liệt kê trạng thái → xác định sự kiện → thêm guard condition → vẽ điểm đầu/cuối → kiểm tra) và liệt kê các lỗi phổ biến theo nhóm: đặt tên trạng thái sai, thiếu guard condition, trạng thái không thoát được, tên sự kiện không nhất quán.
+Kiểm chứng: AI trình bày chính xác. Tôi xác nhận lỗi đặt tên trạng thái bằng hành động (ví dụ "Gửi email" thay vì "Đã gửi") là lỗi tôi hay mắc. Tôi quyết định lưu checklist lỗi này để tự kiểm tra khi vẽ.</t>
+  </si>
+  <si>
+    <t>AI trình bày tổng quan 4 thành phần: định nghĩa trạng thái &amp; chuyển tiếp, các ký hiệu chuẩn UML (điểm đầu, trạng thái, mũi tên, điểm cuối), ngữ cảnh ứng dụng, và ví dụ vòng đời đơn hàng kèm sơ đồ minh họa.
+Quyết định: Tôi nhận ra AI trình bày đúng cấu trúc học State Diagram. Tôi chọn giữ toàn bộ nội dung vì bao quát đủ 4 giai đoạn cần học.</t>
   </si>
 </sst>
 </file>
@@ -1169,4 +1208,104 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD995D44-6FCB-4323-BF88-7AE71EDC663A}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.3984375" customWidth="1"/>
+    <col min="2" max="2" width="31.59765625" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="39.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="138" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="138" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenThiAnThuyen.xlsx
+++ b/AI Audit Log_NguyenThiAnThuyen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\swd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54EE732-AF8A-4F19-9981-723E03CDBFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6913DA-955B-4BCC-962C-B16BF645CC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="6" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="week3" sheetId="4" r:id="rId4"/>
     <sheet name="week4" sheetId="5" r:id="rId5"/>
     <sheet name="week5" sheetId="6" r:id="rId6"/>
+    <sheet name="week6" sheetId="7" r:id="rId7"/>
+    <sheet name="week7" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="89">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -290,6 +292,47 @@
   <si>
     <t>AI trình bày tổng quan 4 thành phần: định nghĩa trạng thái &amp; chuyển tiếp, các ký hiệu chuẩn UML (điểm đầu, trạng thái, mũi tên, điểm cuối), ngữ cảnh ứng dụng, và ví dụ vòng đời đơn hàng kèm sơ đồ minh họa.
 Quyết định: Tôi nhận ra AI trình bày đúng cấu trúc học State Diagram. Tôi chọn giữ toàn bộ nội dung vì bao quát đủ 4 giai đoạn cần học.</t>
+  </si>
+  <si>
+    <t>Nhận diện kiến trúc Activity Diagram</t>
+  </si>
+  <si>
+    <t>"Tìm hiểu về Activity Diagram UML: định nghĩa, ký hiệu (action, decision, fork/join, swimlane), phân biệt với flowchart, ví dụ minh họa"</t>
+  </si>
+  <si>
+    <t>AI trình bày đầy đủ 6 ký hiệu chính và so sánh với flowchart thông thường.
+Quyết định: Tôi đặc biệt chú ý ký hiệu Fork/Join vì đây là điểm mới so với flowchart thông thường.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân biệt: Decision (hình thoi) = 1 vào ≥2 ra theo điều kiện; Fork = 1 vào nhiều ra song song; Join = nhiều vào 1 ra, chờ tất cả hoàn thành.
+Kiểm chứng: Tôi xác nhận Fork/Join phải đi theo cặp. Ghi chú: 'Fork không có Join = deadlock logic'.</t>
+  </si>
+  <si>
+    <t>Phân biệt Decision node và Fork/Join node trong Activity Diagram. Ví dụ thực tế và lưu ý khi vẽ.</t>
+  </si>
+  <si>
+    <t>Cách sử dụng Swimlane trong Activity Diagram để phân chia trách nhiệm: Khách hàng, Hệ thống, Ngân hàng trong quy trình thanh toán online.</t>
+  </si>
+  <si>
+    <t>AI trình bày đúng cách chia swimlane theo chiều dọc, mỗi lane chứa action của một actor.
+Kiểm chứng: Tôi phát hiện đã đặt nhầm 'Xác nhận thanh toán' vào lane Khách hàng thay vì Hệ thống. Tôi sửa lại và nắm rõ nguyên tắc.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn dùng Decision node sau bước có thể thất bại với nhánh [thành công] và [thất bại].
+Kiểm chứng: Tôi xác nhận không cần ký hiệu đặc biệt cho exception — chỉ cần Decision node với guard condition rõ ràng. Tôi cập nhật lại diagram bài tập.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tạo diagram với 2 swimlane, Decision node kiểm tra email và tài khoản, Fork/Join cho gửi email và cập nhật database song song.
+Kiểm chứng: Tôi tự vẽ lại — phát hiện quên Join node sau Fork. Tôi bổ sung đúng cặp Fork/Join và xác nhận diagram logic chính xác, đúng chuẩn UML.</t>
+  </si>
+  <si>
+    <t>Vẽ Activity Diagram cho quy trình đăng ký tài khoản: nhập thông tin → xác thực email → kiểm tra trùng lặp → tạo tài khoản → gửi email chào mừng. Dùng swimlane cho Người dùng và Hệ thống.</t>
+  </si>
+  <si>
+    <t>Làm thế nào để mô tả exception flow trong Activity Diagram? Ví dụ: thanh toán thất bại trong quy trình đặt hàng.</t>
+  </si>
+  <si>
+    <t>Nhận diện luồng hoạt động &amp; ngoại lệ</t>
   </si>
 </sst>
 </file>
@@ -802,7 +845,7 @@
     <col min="1" max="1" width="12.59765625" customWidth="1"/>
     <col min="2" max="2" width="29.296875" customWidth="1"/>
     <col min="3" max="3" width="33.796875" customWidth="1"/>
-    <col min="4" max="4" width="36.19921875" customWidth="1"/>
+    <col min="4" max="4" width="54.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -820,7 +863,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="165.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -834,7 +877,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="179.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -862,7 +905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="151.80000000000001" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -876,7 +919,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="179.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1308,4 +1351,119 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A8A2E4B-432D-4662-B67C-05427A262A1F}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.3984375" customWidth="1"/>
+    <col min="2" max="2" width="21.796875" customWidth="1"/>
+    <col min="3" max="3" width="27.296875" customWidth="1"/>
+    <col min="4" max="4" width="49.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="69" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="69" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="69" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="69" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292BEB1D-8FB4-46C8-8A50-6AE7F831B099}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.69921875" customWidth="1"/>
+    <col min="2" max="2" width="32.8984375" customWidth="1"/>
+    <col min="3" max="3" width="32.796875" customWidth="1"/>
+    <col min="4" max="4" width="39.8984375" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenThiAnThuyen.xlsx
+++ b/AI Audit Log_NguyenThiAnThuyen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\swd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6913DA-955B-4BCC-962C-B16BF645CC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278EB45B-05E6-4E26-9009-726E74A3FA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="6" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="7" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="109">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -333,6 +333,72 @@
   </si>
   <si>
     <t>Nhận diện luồng hoạt động &amp; ngoại lệ</t>
+  </si>
+  <si>
+    <t>Khái niệm
+Component Diagram</t>
+  </si>
+  <si>
+    <t>Ký hiệu
+Component Diagram</t>
+  </si>
+  <si>
+    <t>Cách vẽ
+Component Diagram</t>
+  </si>
+  <si>
+    <t>Lưu ý Ký hiệu &amp; Nội dung</t>
+  </si>
+  <si>
+    <t>Lưu ý
+Quan hệ &amp; Layout</t>
+  </si>
+  <si>
+    <t>Ví dụ minh họa
+Hệ thống Web 3 tầng</t>
+  </si>
+  <si>
+    <t>So sánh
+Loại Diagram</t>
+  </si>
+  <si>
+    <t>Component Diagram khác Class Diagram và Deployment Diagram như thế nào?</t>
+  </si>
+  <si>
+    <t>Vẽ component diagram minh họa hệ thống web gồm React App, API Gateway, Auth Service, Database và Cache. Giải thích từng thành phần và interface.</t>
+  </si>
+  <si>
+    <t>Những lưu ý về quan hệ dependency và cách sắp xếp layout trong component diagram?</t>
+  </si>
+  <si>
+    <t>Những lưu ý quan trọng về ký hiệu khi vẽ component diagram là gì?</t>
+  </si>
+  <si>
+    <t>Hướng dẫn các bước cụ thể để vẽ component diagram từ đầu cho một hệ thống web?</t>
+  </si>
+  <si>
+    <t>Các ký hiệu cơ bản trong component diagram gồm những gì? (component, provided interface, required interface, dependency, subsystem)</t>
+  </si>
+  <si>
+    <t>UML component diagram là gì? Mục đích và khi nào sử dụng?</t>
+  </si>
+  <si>
+    <t>AI giải thích: Component Diagram là biểu đồ cấu trúc trong UML mô tả tổ chức và quan hệ giữa các thành phần phần mềm. Dùng để thể hiện kiến trúc vật lý, cách các module giao tiếp qua interface, hỗ trợ triển khai và phân chia công việc nhóm. Quyết định: Ghi nhận định nghĩa và mục đích.</t>
+  </si>
+  <si>
+    <t>AI liệt kê 5 ký hiệu chính: (1) Component – hình chữ nhật có icon tab nhỏ, stereotype «component»; (2) Provided Interface – lollipop (vòng tròn); (3) Required Interface – socket (bán nguyệt); (4) Dependency – mũi tên nét đứt với «use»; (5) Package/Subsystem – hình chữ nhật bao ngoài. Quyết định: Áp dụng đúng ký hiệu chuẩn UML 2.x.</t>
+  </si>
+  <si>
+    <t>AI hướng dẫn 5 bước: (1) Xác định components độc lập; (2) Xác định provided/required interface từng component; (3) Xác định quan hệ dependency; (4) Nhóm vào subsystem; (5) Vẽ, kiểm tra chiều mũi tên và tránh circular dependency. Quyết định: Áp dụng quy trình 5 bước cho bài thực hành.</t>
+  </si>
+  <si>
+    <t>AI nêu các lưu ý: Icon component (tab nhỏ) phải rõ; Provided/Required interface không được nhầm; Stereotype phải dùng guillemet «»; Mỗi component phải độc lập, có thể thay thế riêng; Không vẽ từng class vào đây (dành cho Class Diagram); Tên component là danh từ ngắn gọn. Quyết định: Ghi nhớ và áp dụng.</t>
+  </si>
+  <si>
+    <t>AI hướng dẫn: Dependency («use», nét đứt) chỉ chiều phụ thuộc, không phải data flow; Không nối trực tiếp 2 component nếu có interface; Tránh circular dependency (A→B và B→A); Nhóm component liên quan vào subsystem; Sắp xếp theo tầng Client→Server→Database; Không để nhiều mũi tên chéo nhau. Quyết định: Thiết kế diagram theo chuẩn kiến trúc phân tầng.</t>
+  </si>
+  <si>
+    <t>AI so sánh: Component Diagram – tập trung vào module/thành phần, mức kiến trúc hệ thống; Class Diagram – tập trung vào class và object, mức logic code; Deployment Diagram – tập trung vào phần cứng/server, mức hạ tầng triển khai. Quyết định: Hiểu rõ phạm vi áp dụng từng loại để chọn đúng khi làm bài.</t>
   </si>
 </sst>
 </file>
@@ -1455,15 +1521,128 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292BEB1D-8FB4-46C8-8A50-6AE7F831B099}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.69921875" customWidth="1"/>
     <col min="2" max="2" width="32.8984375" customWidth="1"/>
     <col min="3" max="3" width="32.796875" customWidth="1"/>
-    <col min="4" max="4" width="39.8984375" customWidth="1"/>
+    <col min="4" max="4" width="56.69921875" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AI Audit Log_NguyenThiAnThuyen.xlsx
+++ b/AI Audit Log_NguyenThiAnThuyen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\swd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278EB45B-05E6-4E26-9009-726E74A3FA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16A6254-D1CC-43E5-850A-506121F8BEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="7" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="week5" sheetId="6" r:id="rId6"/>
     <sheet name="week6" sheetId="7" r:id="rId7"/>
     <sheet name="week7" sheetId="8" r:id="rId8"/>
+    <sheet name="week8" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="119">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -399,6 +400,39 @@
   </si>
   <si>
     <t>AI so sánh: Component Diagram – tập trung vào module/thành phần, mức kiến trúc hệ thống; Class Diagram – tập trung vào class và object, mức logic code; Deployment Diagram – tập trung vào phần cứng/server, mức hạ tầng triển khai. Quyết định: Hiểu rõ phạm vi áp dụng từng loại để chọn đúng khi làm bài.</t>
+  </si>
+  <si>
+    <t>Tìm hiểu khái niệm Context Diagram</t>
+  </si>
+  <si>
+    <t>"nêu khái niệm cơ bản về context diagram và state diagram bao gồm cả cách vẽ"</t>
+  </si>
+  <si>
+    <t>AI trình bày Context Diagram là sơ đồ DFD mức 0, thể hiện hệ thống như 1 khối duy nhất, không đi vào chi tiết bên trong; gồm 3 thành phần: hệ thống, tác nhân ngoài, luồng dữ liệu.
+Quyết định: Tôi ghi nhận nguyên tắc chỉ vẽ ranh giới hệ thống, không vẽ tiến trình con ở mức context.</t>
+  </si>
+  <si>
+    <t>AI liệt kê ký hiệu: hệ thống = hình tròn/chữ nhật bo góc ở trung tâm; tác nhân ngoài = hình chữ nhật; luồng dữ liệu = mũi tên có nhãn ngắn gọn, có chiều rõ ràng.
+Kiểm chứng: Tôi xác nhận quy tắc quan trọng nhất là tác nhân chỉ nối với hệ thống trung tâm, không nối chéo giữa các tác nhân với nhau.</t>
+  </si>
+  <si>
+    <t>Yêu cầu làm rõ cách vẽ Context Diagram</t>
+  </si>
+  <si>
+    <t>Ký hiệu &amp; quy tắc vẽ Context Diagram</t>
+  </si>
+  <si>
+    <t>Tìm hiểu khái niệm State Diagram</t>
+  </si>
+  <si>
+    <t>Yêu cầu nêu khái niệm cơ bản về State Diagram</t>
+  </si>
+  <si>
+    <t>AI giải thích State Diagram (UML) mô tả vòng đời của 1 đối tượng qua các trạng thái (state) và sự chuyển đổi (transition) khi có sự kiện xảy ra.
+Quyết định: Tôi phân biệt được State Diagram khác Activity Diagram ở chỗ tập trung vào 'trạng thái tồn tại' chứ không phải 'luồng hành động'.</t>
+  </si>
+  <si>
+    <t>Yêu cầu làm rõ cách vẽ State Diagram</t>
   </si>
 </sst>
 </file>
@@ -1544,7 +1578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -1558,7 +1592,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -1572,7 +1606,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -1586,7 +1620,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -1600,7 +1634,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -1614,7 +1648,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -1628,7 +1662,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -1641,6 +1675,98 @@
       <c r="D8" s="7" t="s">
         <v>108</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA46EAF-F7B7-4929-B71E-593A00FFB835}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.09765625" customWidth="1"/>
+    <col min="2" max="2" width="36.09765625" customWidth="1"/>
+    <col min="3" max="3" width="46.296875" customWidth="1"/>
+    <col min="4" max="4" width="45.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="104.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="103.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="118.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
